--- a/data/trans_orig/P1432-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1432-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2007</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,82 +732,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4581</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>916</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6824</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>460665</t>
+          <t>462908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>956953</t>
+          <t>956948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>730464</t>
+          <t>730444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>619486</t>
+          <t>619467</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1354067</t>
+          <t>1352371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631783</t>
+          <t>630438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>683702</t>
+          <t>683007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1318247</t>
+          <t>1317736</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327376</t>
+          <t>1327371</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>513639</t>
+          <t>513613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>506231</t>
+          <t>506053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>514659</t>
+          <t>514664</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1022077</t>
+          <t>1021621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1032063</t>
+          <t>1032057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17216</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>22375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>376473</t>
+          <t>376860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>385054</t>
+          <t>385004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386660</t>
+          <t>386770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399710</t>
+          <t>399786</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>767888</t>
+          <t>768321</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>783396</t>
+          <t>783580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19584</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>33375</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274299</t>
+          <t>274666</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287089</t>
+          <t>287046</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>323350</t>
+          <t>322734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>336484</t>
+          <t>337029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>602873</t>
+          <t>602142</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>621199</t>
+          <t>620597</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9533</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24416</t>
+          <t>24651</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13365</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>31929</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27027</t>
+          <t>25497</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>51132</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185467</t>
+          <t>185232</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200655</t>
+          <t>200350</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>300318</t>
+          <t>301979</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320543</t>
+          <t>320712</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>491572</t>
+          <t>492659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>516764</t>
+          <t>518294</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37704</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65998</t>
+          <t>68044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70998</t>
+          <t>68992</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106205</t>
+          <t>106354</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3227563</t>
+          <t>3227151</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3250501</t>
+          <t>3250063</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3313199</t>
+          <t>3311153</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3341493</t>
+          <t>3340889</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6549536</t>
+          <t>6549387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6584743</t>
+          <t>6586749</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2012</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,97 +3711,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4054,97 +4054,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>685112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>687087</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>610255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1295331</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1297342</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>675189</t>
+          <t>674456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>703644</t>
+          <t>703060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1381752</t>
+          <t>1380584</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1390419</t>
+          <t>1390410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>608487</t>
+          <t>607612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>604840</t>
+          <t>605107</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>613284</t>
+          <t>613291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1217456</t>
+          <t>1217440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1226882</t>
+          <t>1226860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>18641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21272</t>
+          <t>21708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>423106</t>
+          <t>422106</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>429037</t>
+          <t>429159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442571</t>
+          <t>442608</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>855957</t>
+          <t>855521</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>870956</t>
+          <t>870980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>20302</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33767</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287358</t>
+          <t>286323</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>304597</t>
+          <t>304372</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>335046</t>
+          <t>333694</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>349103</t>
+          <t>349143</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>630015</t>
+          <t>628817</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>651370</t>
+          <t>650602</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22537</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44563</t>
+          <t>45494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>26208</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50981</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238745</t>
+          <t>239724</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247957</t>
+          <t>248027</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>343307</t>
+          <t>342376</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>365333</t>
+          <t>365434</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>586740</t>
+          <t>587006</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>611829</t>
+          <t>611513</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>34740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44781</t>
+          <t>43029</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74842</t>
+          <t>75272</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62231</t>
+          <t>64090</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>100120</t>
+          <t>101372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3389650</t>
+          <t>3392039</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3412704</t>
+          <t>3413214</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3479148</t>
+          <t>3478718</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3509209</t>
+          <t>3510961</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6880649</t>
+          <t>6879397</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6918538</t>
+          <t>6916679</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2016</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,97 +6690,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7033,97 +7033,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>563544</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1152108</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1154040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>653619</t>
+          <t>653563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1322220</t>
+          <t>1321834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1329603</t>
+          <t>1329605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>11051</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>641668</t>
+          <t>640860</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639848</t>
+          <t>639463</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648055</t>
+          <t>648041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1283001</t>
+          <t>1284074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1293145</t>
+          <t>1293174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>16683</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19628</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471593</t>
+          <t>471160</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>478720</t>
+          <t>480166</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>492424</t>
+          <t>492519</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>955139</t>
+          <t>955255</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>970071</t>
+          <t>969279</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20207</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>325823</t>
+          <t>326512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333384</t>
+          <t>333387</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>361131</t>
+          <t>360943</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>373818</t>
+          <t>373707</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>691885</t>
+          <t>691271</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>705450</t>
+          <t>705371</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20549</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38761</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26402</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54227</t>
+          <t>53800</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236449</t>
+          <t>237060</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>250163</t>
+          <t>249875</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>361408</t>
+          <t>359067</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382866</t>
+          <t>382593</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>602940</t>
+          <t>603367</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>630765</t>
+          <t>629018</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26742</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>38462</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65875</t>
+          <t>69353</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52845</t>
+          <t>53794</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88229</t>
+          <t>87626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3367608</t>
+          <t>3368071</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3383140</t>
+          <t>3383759</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3478667</t>
+          <t>3475189</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3506797</t>
+          <t>3506080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6850663</t>
+          <t>6851266</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6886047</t>
+          <t>6885098</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1432-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1432-Edad-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>462908</t>
+          <t>462871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>956948</t>
+          <t>956962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>730444</t>
+          <t>730436</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>619467</t>
+          <t>619456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1352371</t>
+          <t>1353677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>630438</t>
+          <t>631387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>683007</t>
+          <t>682632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1317736</t>
+          <t>1318773</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327371</t>
+          <t>1327391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>513613</t>
+          <t>512714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>506053</t>
+          <t>505776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1021621</t>
+          <t>1022323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1032057</t>
+          <t>1032679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>17284</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22375</t>
+          <t>21774</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>376860</t>
+          <t>377222</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>385004</t>
+          <t>385042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>386770</t>
+          <t>386702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399786</t>
+          <t>399035</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>768321</t>
+          <t>768922</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>783580</t>
+          <t>782943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33375</t>
+          <t>35125</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274666</t>
+          <t>274242</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287046</t>
+          <t>287142</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>322734</t>
+          <t>323295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>337029</t>
+          <t>337111</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>602142</t>
+          <t>600392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>620597</t>
+          <t>620483</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9533</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13697</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31929</t>
+          <t>34885</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25497</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>51647</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185232</t>
+          <t>184975</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200350</t>
+          <t>200713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>301979</t>
+          <t>299023</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320712</t>
+          <t>320211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>492659</t>
+          <t>492144</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>518294</t>
+          <t>517006</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>26081</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68044</t>
+          <t>66395</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68992</t>
+          <t>68472</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106354</t>
+          <t>106966</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3227151</t>
+          <t>3226755</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3250063</t>
+          <t>3250462</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3311153</t>
+          <t>3312802</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3340889</t>
+          <t>3341588</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6549387</t>
+          <t>6548775</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6586749</t>
+          <t>6587269</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>674456</t>
+          <t>674890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>703060</t>
+          <t>701987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1380584</t>
+          <t>1382565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1390410</t>
+          <t>1390434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607612</t>
+          <t>607582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>605107</t>
+          <t>604904</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>613291</t>
+          <t>613288</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1217440</t>
+          <t>1217674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1226860</t>
+          <t>1226934</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422106</t>
+          <t>422117</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>429159</t>
+          <t>429847</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442608</t>
+          <t>442614</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>855521</t>
+          <t>856426</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>870980</t>
+          <t>870939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>20770</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20302</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>34375</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286323</t>
+          <t>289016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>304372</t>
+          <t>304393</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>333694</t>
+          <t>336107</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>349143</t>
+          <t>349898</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>628817</t>
+          <t>629407</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>650602</t>
+          <t>651065</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22436</t>
+          <t>22753</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45494</t>
+          <t>46027</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>27102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50715</t>
+          <t>51620</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>239724</t>
+          <t>238896</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248027</t>
+          <t>248033</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>342376</t>
+          <t>341843</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>365434</t>
+          <t>365117</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>587006</t>
+          <t>586101</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>611513</t>
+          <t>610619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13565</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34740</t>
+          <t>35835</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43029</t>
+          <t>43559</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75272</t>
+          <t>73835</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64090</t>
+          <t>62191</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>101372</t>
+          <t>100231</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3392039</t>
+          <t>3390944</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3413214</t>
+          <t>3412516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3478718</t>
+          <t>3480155</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3510961</t>
+          <t>3510431</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6879397</t>
+          <t>6880538</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6916679</t>
+          <t>6918578</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>653563</t>
+          <t>653552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660509</t>
+          <t>660503</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1321834</t>
+          <t>1322763</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1329605</t>
+          <t>1329601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>640860</t>
+          <t>641274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639463</t>
+          <t>638732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648041</t>
+          <t>648033</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1284074</t>
+          <t>1283944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1293174</t>
+          <t>1293152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19512</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471160</t>
+          <t>472726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>480166</t>
+          <t>480119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>492519</t>
+          <t>492496</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>955255</t>
+          <t>955078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>969279</t>
+          <t>970031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>15903</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20821</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>326512</t>
+          <t>325643</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>360943</t>
+          <t>361859</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>373707</t>
+          <t>373792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>691271</t>
+          <t>691794</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>705371</t>
+          <t>705325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7123</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41102</t>
+          <t>40891</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28149</t>
+          <t>27952</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53800</t>
+          <t>54607</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237060</t>
+          <t>236966</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>249875</t>
+          <t>250204</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>359067</t>
+          <t>359278</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382593</t>
+          <t>382729</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>603367</t>
+          <t>602560</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>629018</t>
+          <t>629215</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38462</t>
+          <t>35140</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69353</t>
+          <t>67268</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53794</t>
+          <t>54011</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87626</t>
+          <t>88710</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3368071</t>
+          <t>3366565</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3383759</t>
+          <t>3383873</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3475189</t>
+          <t>3477274</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3506080</t>
+          <t>3509402</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6851266</t>
+          <t>6850182</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6885098</t>
+          <t>6884881</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
